--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_45.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5530014.233194849</v>
+        <v>5489672.974356779</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645784</v>
+        <v>6767152.318645789</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645784</v>
+        <v>6767152.318645789</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517485</v>
+        <v>2916902.906517486</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517485</v>
+        <v>2916902.906517486</v>
       </c>
     </row>
     <row r="11">
@@ -657,37 +657,37 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>96.36700516145162</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>748.0913712690564</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>297.9910820919849</v>
+        <v>611.1455837021076</v>
       </c>
       <c r="N2" t="n">
         <v>194.5855355810472</v>
@@ -702,7 +702,7 @@
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>494.8481678023229</v>
@@ -717,13 +717,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>331.942867366362</v>
       </c>
       <c r="X2" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>57.72562438342279</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -787,10 +787,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>5.357765217513816</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U3" t="n">
-        <v>241.4182054861266</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>114.9691617061062</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269246</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -900,28 +900,28 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>96.36700516145173</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690067</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L5" t="n">
-        <v>814</v>
+        <v>650.9664887921592</v>
       </c>
       <c r="M5" t="n">
         <v>297.9910820919849</v>
@@ -930,10 +930,10 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>814</v>
-      </c>
-      <c r="P5" t="n">
-        <v>216.0296191332252</v>
       </c>
       <c r="Q5" t="n">
         <v>370.9706110579117</v>
@@ -942,10 +942,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>187.4578006767583</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>167.1158402638075</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>116.4884513832911</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>297.3920501269273</v>
+        <v>297.3920501269233</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>324.6901055126944</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C8" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1140,10 +1140,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>246.4481648441361</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1167,10 +1167,10 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
+        <v>650.9664887921559</v>
+      </c>
+      <c r="P8" t="n">
         <v>814</v>
-      </c>
-      <c r="P8" t="n">
-        <v>313.1545016101224</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
@@ -1179,7 +1179,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1191,13 +1191,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>131.9860885083954</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1261,19 +1261,19 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>90.0987672932513</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617060988</v>
       </c>
       <c r="N10" t="n">
-        <v>141.9749974174559</v>
+        <v>171.1850752716849</v>
       </c>
       <c r="O10" t="n">
         <v>240.445564079015</v>
@@ -1374,16 +1374,16 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.03275099961586193</v>
       </c>
       <c r="F11" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1422,13 +1422,13 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>417.6585133970744</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>367.2818334606677</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>45.14518808597777</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1611,13 +1611,13 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>67.57968198731129</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>157.0096587035274</v>
@@ -1659,7 +1659,7 @@
         <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>159.6803166420367</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
         <v>378.8510241668239</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>36.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>23.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>269.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1802,13 +1802,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="Q16" t="n">
-        <v>141.2616799508307</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>36.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1851,10 +1851,10 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934258</v>
       </c>
       <c r="G17" t="n">
-        <v>124.3267636724302</v>
+        <v>124.7573722870162</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>222.6291430547296</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R19" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>369.327645604236</v>
+        <v>238.6861349114283</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>359.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>312.8512248460818</v>
+        <v>313.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>232.3174326828064</v>
+        <v>231.8868240682205</v>
       </c>
     </row>
     <row r="24">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>330.1734149513624</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>238.6861349114283</v>
       </c>
       <c r="R25" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>81.5575639242365</v>
+        <v>189.411675845388</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
         <v>269.8481678023229</v>
@@ -2613,7 +2613,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>367.2818334606677</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>233.8881446236372</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>189.411675845388</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>91.3978464201515</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2847,7 +2847,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>413.3734759809475</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>345.920735428856</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3045,31 +3045,31 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>8.45659138541424</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589747</v>
+        <v>377.738269658977</v>
       </c>
       <c r="K32" t="n">
-        <v>10.23281455319705</v>
+        <v>505.4012214189849</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000412</v>
+        <v>256.9910820920281</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810884</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="O32" t="n">
-        <v>598.5739533769238</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000412</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579529</v>
+        <v>329.9706110579551</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3221,19 +3221,19 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q34" t="n">
-        <v>387.1252532547696</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3285,28 +3285,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>757.6173000000474</v>
+        <v>377.7382696589843</v>
       </c>
       <c r="K35" t="n">
-        <v>10.23281455300108</v>
+        <v>727.1079320762562</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>256.9910820920331</v>
+        <v>256.9910820920354</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000484</v>
+        <v>551.2932893429986</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000484</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>115.2893765249316</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.9706110579601</v>
+        <v>329.9706110579624</v>
       </c>
       <c r="R35" t="n">
         <v>8.456591385414804</v>
@@ -3455,19 +3455,19 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>225.4675834971127</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>109.2047614405436</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>190.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>166.9311696284081</v>
+        <v>158.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>119.3391557398498</v>
@@ -3522,31 +3522,31 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>742.2346000000543</v>
+        <v>757.6173000000567</v>
       </c>
       <c r="K38" t="n">
-        <v>773</v>
+        <v>10.23281455286669</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920404</v>
+        <v>773.000000000058</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355810472</v>
+        <v>773.000000000058</v>
       </c>
       <c r="O38" t="n">
-        <v>332.6726665551029</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000545</v>
+        <v>702.2510696749553</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3689,19 +3689,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>275.2581858107217</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
         <v>435.6021279811511</v>
@@ -3735,16 +3735,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>148.1404337297647</v>
+        <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>191.8896287080119</v>
@@ -3753,7 +3753,7 @@
         <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,19 +3783,19 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>8.201637464911718</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>373.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>436.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>425.3734759809475</v>
@@ -3835,7 +3835,7 @@
         <v>119.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4.126385891348534</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>213.7510769620688</v>
+        <v>253.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>98.40326768090138</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>67.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>15.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>154.347044504849</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>13.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3981,10 +3981,10 @@
         <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>104.8036529964224</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>11.21552370913105</v>
       </c>
       <c r="G44" t="n">
         <v>216.7573722870162</v>
@@ -4026,22 +4026,22 @@
         <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>399.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>462.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>442.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,19 +4051,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>174.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>138.7395358750273</v>
@@ -4102,22 +4102,22 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>249.1794707934943</v>
+        <v>224.1835966301003</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>218.3577652175138</v>
       </c>
       <c r="U45" t="n">
         <v>213.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>232.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>212.3913927661343</v>
@@ -4184,16 +4184,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,37 +4297,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>795.9528038842302</v>
+        <v>954.8509932204727</v>
       </c>
       <c r="C2" t="n">
-        <v>341.9380783862565</v>
+        <v>904.876671762903</v>
       </c>
       <c r="D2" t="n">
-        <v>331.4944867298426</v>
+        <v>894.4330801064891</v>
       </c>
       <c r="E2" t="n">
-        <v>327.0871234905813</v>
+        <v>485.9853128268238</v>
       </c>
       <c r="F2" t="n">
-        <v>322.1481045935997</v>
+        <v>481.0462939298421</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8076953396081</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>115.3321502332764</v>
+        <v>431.6498286273397</v>
       </c>
       <c r="L2" t="n">
-        <v>98.96992801105404</v>
+        <v>415.2876064051173</v>
       </c>
       <c r="M2" t="n">
         <v>603.828834988847</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S2" t="n">
-        <v>2502.740639767053</v>
+        <v>2756.153365856239</v>
       </c>
       <c r="T2" t="n">
-        <v>2314.179446101837</v>
+        <v>2567.592172191023</v>
       </c>
       <c r="U2" t="n">
-        <v>2062.440762719402</v>
+        <v>2315.853488808588</v>
       </c>
       <c r="V2" t="n">
-        <v>1830.268011035741</v>
+        <v>2083.680737124928</v>
       </c>
       <c r="W2" t="n">
-        <v>1589.486722166097</v>
+        <v>1748.38491150234</v>
       </c>
       <c r="X2" t="n">
-        <v>991.2222439229987</v>
+        <v>1554.160837299645</v>
       </c>
       <c r="Y2" t="n">
-        <v>878.7803927282448</v>
+        <v>1037.678582064487</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="C3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="D3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="E3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="F3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="G3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="H3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="I3" t="n">
         <v>65.12</v>
@@ -4421,31 +4421,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.552420368536</v>
+        <v>1162.243708870129</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.791008962092</v>
+        <v>1013.482297463685</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.554645361474</v>
+        <v>946.2459338630676</v>
       </c>
       <c r="T3" t="n">
-        <v>999.1427613033796</v>
+        <v>536.7936457645687</v>
       </c>
       <c r="U3" t="n">
-        <v>755.2859880850699</v>
+        <v>132.5407571179154</v>
       </c>
       <c r="V3" t="n">
-        <v>740.6287484976758</v>
+        <v>117.8835175305213</v>
       </c>
       <c r="W3" t="n">
-        <v>707.9286041443137</v>
+        <v>85.18337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>687.8652309671545</v>
+        <v>65.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>958.9851581225348</v>
+        <v>523.809767390122</v>
       </c>
       <c r="C4" t="n">
-        <v>958.9851581225348</v>
+        <v>649.8117732085578</v>
       </c>
       <c r="D4" t="n">
-        <v>958.9851581225348</v>
+        <v>649.8117732085578</v>
       </c>
       <c r="E4" t="n">
-        <v>1061.518235171307</v>
+        <v>767.6406774199709</v>
       </c>
       <c r="F4" t="n">
-        <v>1061.518235171307</v>
+        <v>892.0016500119063</v>
       </c>
       <c r="G4" t="n">
-        <v>1214.924801058193</v>
+        <v>1045.408215898792</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.924801058193</v>
+        <v>1214.924801058189</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994276</v>
+        <v>1436.057679994272</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994276</v>
+        <v>1436.057679994272</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931144</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931144</v>
+        <v>1522.636630943485</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.786518415657</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.87230096951</v>
       </c>
       <c r="O4" t="n">
-        <v>1014.503122964673</v>
+        <v>984.99799381899</v>
       </c>
       <c r="P4" t="n">
-        <v>724.1517115219688</v>
+        <v>694.6465823762856</v>
       </c>
       <c r="Q4" t="n">
-        <v>395.0211393749001</v>
+        <v>365.5160102292168</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4509,22 +4509,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V4" t="n">
-        <v>735.8185197772104</v>
+        <v>128.7522107851203</v>
       </c>
       <c r="W4" t="n">
-        <v>735.8185197772104</v>
+        <v>300.6431290447977</v>
       </c>
       <c r="X4" t="n">
-        <v>735.8185197772104</v>
+        <v>300.6431290447977</v>
       </c>
       <c r="Y4" t="n">
-        <v>847.2278204562427</v>
+        <v>412.0524297238299</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1199.993207924634</v>
+        <v>1106.448124213083</v>
       </c>
       <c r="C5" t="n">
-        <v>1150.018886467065</v>
+        <v>1056.473802755514</v>
       </c>
       <c r="D5" t="n">
-        <v>1139.575294810651</v>
+        <v>1046.0302110991</v>
       </c>
       <c r="E5" t="n">
-        <v>731.1275275309855</v>
+        <v>1041.622847859839</v>
       </c>
       <c r="F5" t="n">
-        <v>726.1885086340038</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G5" t="n">
-        <v>628.8480993800122</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4558,22 +4558,22 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K5" t="n">
-        <v>1155.766108953703</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L5" t="n">
-        <v>1139.40388673148</v>
+        <v>921.192150233273</v>
       </c>
       <c r="M5" t="n">
-        <v>1644.262793709273</v>
+        <v>1426.051057211066</v>
       </c>
       <c r="N5" t="n">
-        <v>2253.571747667811</v>
+        <v>2035.360011169604</v>
       </c>
       <c r="O5" t="n">
-        <v>2237.209525445593</v>
+        <v>2841.220011169604</v>
       </c>
       <c r="P5" t="n">
         <v>2824.857788947385</v>
@@ -4585,25 +4585,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2906.781043807457</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T5" t="n">
-        <v>2718.219850142241</v>
+        <v>2220.634362390286</v>
       </c>
       <c r="U5" t="n">
-        <v>2466.481166759806</v>
+        <v>1968.895679007851</v>
       </c>
       <c r="V5" t="n">
-        <v>2234.308415076146</v>
+        <v>1736.722927324191</v>
       </c>
       <c r="W5" t="n">
-        <v>1993.527126206502</v>
+        <v>1495.941638454547</v>
       </c>
       <c r="X5" t="n">
-        <v>1799.303052003807</v>
+        <v>1301.717564251852</v>
       </c>
       <c r="Y5" t="n">
-        <v>1282.820796768649</v>
+        <v>1189.275713057098</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>429.8673863086054</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>65.12</v>
+        <v>762.705640524864</v>
       </c>
       <c r="D6" t="n">
-        <v>65.12</v>
+        <v>411.2534315372855</v>
       </c>
       <c r="E6" t="n">
         <v>65.12</v>
@@ -4673,16 +4673,16 @@
         <v>998.9302766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>580.2326330693322</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>547.5324887159701</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>429.8673863086054</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>429.8673863086054</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>498.7330996970377</v>
+        <v>65.12</v>
       </c>
       <c r="C7" t="n">
-        <v>624.7351055154735</v>
+        <v>175.4088884311052</v>
       </c>
       <c r="D7" t="n">
-        <v>738.0542496404736</v>
+        <v>288.7280325561053</v>
       </c>
       <c r="E7" t="n">
-        <v>738.0542496404736</v>
+        <v>406.5569367675183</v>
       </c>
       <c r="F7" t="n">
-        <v>862.4152222324091</v>
+        <v>530.9179093594538</v>
       </c>
       <c r="G7" t="n">
-        <v>1015.821788119294</v>
+        <v>684.324475246339</v>
       </c>
       <c r="H7" t="n">
-        <v>1185.338373278692</v>
+        <v>853.8410604057366</v>
       </c>
       <c r="I7" t="n">
-        <v>1185.338373278692</v>
+        <v>1074.973939341819</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931143</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943487</v>
+        <v>1522.636630943483</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415659</v>
+        <v>1400.786518415655</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969513</v>
+        <v>1227.872300969509</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189928</v>
+        <v>984.9979938189887</v>
       </c>
       <c r="P7" t="n">
-        <v>694.6465823762883</v>
+        <v>694.6465823762842</v>
       </c>
       <c r="Q7" t="n">
-        <v>365.5160102292195</v>
+        <v>365.5160102292155</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="U7" t="n">
-        <v>175.8113904131667</v>
+        <v>65.12</v>
       </c>
       <c r="V7" t="n">
-        <v>175.8113904131667</v>
+        <v>65.12</v>
       </c>
       <c r="W7" t="n">
-        <v>347.7023086728442</v>
+        <v>65.12</v>
       </c>
       <c r="X7" t="n">
-        <v>498.7330996970377</v>
+        <v>65.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>498.7330996970377</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="8">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>954.8509932204726</v>
+        <v>391.9123998438259</v>
       </c>
       <c r="C8" t="n">
-        <v>500.8362677224989</v>
+        <v>341.9380783862563</v>
       </c>
       <c r="D8" t="n">
-        <v>490.392676066085</v>
+        <v>331.4944867298424</v>
       </c>
       <c r="E8" t="n">
-        <v>485.9853128268237</v>
+        <v>327.0871234905812</v>
       </c>
       <c r="F8" t="n">
-        <v>77.00588988943801</v>
+        <v>322.1481045935995</v>
       </c>
       <c r="G8" t="n">
         <v>73.21056434699739</v>
@@ -4795,22 +4795,22 @@
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K8" t="n">
-        <v>431.6498286273397</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L8" t="n">
-        <v>1237.50982862734</v>
+        <v>1578.734058104141</v>
       </c>
       <c r="M8" t="n">
-        <v>1742.368735605133</v>
+        <v>2083.592965081934</v>
       </c>
       <c r="N8" t="n">
-        <v>2351.677689563671</v>
+        <v>2692.901919040472</v>
       </c>
       <c r="O8" t="n">
-        <v>2335.315467341448</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4822,16 +4822,16 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>2502.740639767053</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2314.179446101837</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U8" t="n">
-        <v>2062.440762719402</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V8" t="n">
-        <v>1830.268011035741</v>
+        <v>2234.308415076146</v>
       </c>
       <c r="W8" t="n">
         <v>1589.486722166097</v>
@@ -4840,7 +4840,7 @@
         <v>1395.262647963403</v>
       </c>
       <c r="Y8" t="n">
-        <v>1282.820796768649</v>
+        <v>878.7803927282447</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.12</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="D9" t="n">
-        <v>65.12</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="E9" t="n">
-        <v>65.12</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="F9" t="n">
-        <v>65.12</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="G9" t="n">
         <v>65.12</v>
@@ -4904,22 +4904,22 @@
         <v>1004.554645361474</v>
       </c>
       <c r="T9" t="n">
-        <v>999.1427613033796</v>
+        <v>595.1023572629756</v>
       </c>
       <c r="U9" t="n">
-        <v>998.9302766971304</v>
+        <v>594.8898726567263</v>
       </c>
       <c r="V9" t="n">
         <v>580.2326330693322</v>
       </c>
       <c r="W9" t="n">
-        <v>489.2237772175632</v>
+        <v>547.5324887159701</v>
       </c>
       <c r="X9" t="n">
-        <v>65.12</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="Y9" t="n">
-        <v>65.12</v>
+        <v>527.4691155388109</v>
       </c>
     </row>
     <row r="10">
@@ -4929,40 +4929,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>614.5199104622992</v>
+        <v>641.6386716015311</v>
       </c>
       <c r="C10" t="n">
-        <v>740.521916280735</v>
+        <v>767.6406774199669</v>
       </c>
       <c r="D10" t="n">
-        <v>853.8410604057351</v>
+        <v>767.6406774199669</v>
       </c>
       <c r="E10" t="n">
-        <v>853.8410604057351</v>
+        <v>767.6406774199669</v>
       </c>
       <c r="F10" t="n">
-        <v>853.8410604057351</v>
+        <v>892.0016500119024</v>
       </c>
       <c r="G10" t="n">
-        <v>853.8410604057351</v>
+        <v>1045.408215898788</v>
       </c>
       <c r="H10" t="n">
-        <v>853.8410604057351</v>
+        <v>1214.924801058185</v>
       </c>
       <c r="I10" t="n">
-        <v>1074.973939341818</v>
+        <v>1436.057679994268</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994269</v>
+        <v>1436.057679994268</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931138</v>
+        <v>1546.422113931137</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943482</v>
+        <v>1546.422113931137</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415654</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
         <v>1257.377430115193</v>
@@ -4986,19 +4986,19 @@
         <v>290.445934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>536.9971268912645</v>
+        <v>291.7864876913916</v>
       </c>
       <c r="V10" t="n">
-        <v>536.9971268912645</v>
+        <v>490.6078805773375</v>
       </c>
       <c r="W10" t="n">
-        <v>536.9971268912645</v>
+        <v>490.6078805773375</v>
       </c>
       <c r="X10" t="n">
-        <v>536.9971268912645</v>
+        <v>641.6386716015311</v>
       </c>
       <c r="Y10" t="n">
-        <v>536.9971268912645</v>
+        <v>641.6386716015311</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>841.3429646241129</v>
+        <v>845.6712852464634</v>
       </c>
       <c r="C11" t="n">
-        <v>614.6009663988665</v>
+        <v>618.9292870212171</v>
       </c>
       <c r="D11" t="n">
-        <v>427.3896979747758</v>
+        <v>431.7180185971264</v>
       </c>
       <c r="E11" t="n">
-        <v>427.3896979747758</v>
+        <v>431.6849367793326</v>
       </c>
       <c r="F11" t="n">
-        <v>245.6830023101174</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="G11" t="n">
-        <v>65.12</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.12</v>
@@ -5038,16 +5038,16 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1166.135479385524</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>1676.984308114459</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>2290.204627889222</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O11" t="n">
-        <v>2450.14</v>
+        <v>3256</v>
       </c>
       <c r="P11" t="n">
         <v>3256</v>
@@ -5065,19 +5065,19 @@
         <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2170.079937619944</v>
+        <v>2591.957223879615</v>
       </c>
       <c r="V11" t="n">
-        <v>1761.139509168607</v>
+        <v>2183.016795428278</v>
       </c>
       <c r="W11" t="n">
-        <v>1761.139509168607</v>
+        <v>1765.467829790957</v>
       </c>
       <c r="X11" t="n">
-        <v>1390.147758198235</v>
+        <v>1394.476078820586</v>
       </c>
       <c r="Y11" t="n">
-        <v>1100.938230235804</v>
+        <v>1105.266550858155</v>
       </c>
     </row>
     <row r="12">
@@ -5108,7 +5108,7 @@
         <v>65.12</v>
       </c>
       <c r="I12" t="n">
-        <v>65.12</v>
+        <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
         <v>215.7971006891144</v>
@@ -5166,52 +5166,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="C13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="D13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="E13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="F13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="G13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="H13" t="n">
-        <v>175.0090463985742</v>
+        <v>173.6223697938169</v>
       </c>
       <c r="I13" t="n">
-        <v>222.8919253346571</v>
+        <v>221.5052487298998</v>
       </c>
       <c r="J13" t="n">
-        <v>410.7256659871084</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="K13" t="n">
-        <v>410.7256659871084</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="L13" t="n">
-        <v>410.7256659871084</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="M13" t="n">
-        <v>410.7256659871084</v>
+        <v>110.7212000868462</v>
       </c>
       <c r="N13" t="n">
-        <v>410.7256659871084</v>
+        <v>110.7212000868462</v>
       </c>
       <c r="O13" t="n">
-        <v>410.7256659871084</v>
+        <v>110.7212000868462</v>
       </c>
       <c r="P13" t="n">
-        <v>410.7256659871084</v>
+        <v>65.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>410.7256659871084</v>
+        <v>65.12</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5229,13 +5229,13 @@
         <v>178.8182646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="Y13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
     </row>
     <row r="14">
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>894.3564187679355</v>
+        <v>653.4059340138207</v>
       </c>
       <c r="C14" t="n">
-        <v>693.8770468053153</v>
+        <v>452.9265620512006</v>
       </c>
       <c r="D14" t="n">
-        <v>532.9284046438509</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>378.015990899539</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>378.015990899539</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="G14" t="n">
         <v>223.7156148520479</v>
@@ -5269,25 +5269,25 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K14" t="n">
-        <v>456.4291130376557</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L14" t="n">
-        <v>1262.289113037656</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M14" t="n">
-        <v>1773.137941766591</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N14" t="n">
-        <v>2386.358261541354</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O14" t="n">
-        <v>2450.14</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3256</v>
@@ -5302,19 +5302,19 @@
         <v>2670.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2509.329226087956</v>
+        <v>2268.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2126.651423899245</v>
+        <v>1885.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>1735.36508452455</v>
+        <v>1494.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1390.635959816805</v>
+        <v>1149.68547506269</v>
       </c>
       <c r="Y14" t="n">
-        <v>1127.689058117001</v>
+        <v>886.7385733628859</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>65.12</v>
+        <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>437.5665201752989</v>
+        <v>471.1013981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>875.2493362696823</v>
+        <v>824.8305228441041</v>
       </c>
       <c r="L15" t="n">
-        <v>1395.089797864882</v>
+        <v>1096.180984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1481.170339607742</v>
+        <v>1182.261526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1862.94062421531</v>
+        <v>1315.541810789732</v>
       </c>
       <c r="O15" t="n">
-        <v>2128.705790033876</v>
+        <v>1803.074262473451</v>
       </c>
       <c r="P15" t="n">
-        <v>2241.235134503383</v>
+        <v>2164.093606942957</v>
       </c>
       <c r="Q15" t="n">
         <v>2241.235134503383</v>
@@ -5403,52 +5403,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>210.6276980209074</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>188.6830044370238</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>188.6830044370238</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>188.6830044370238</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="F16" t="n">
-        <v>165.0639580049613</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="G16" t="n">
-        <v>170.9605238918465</v>
+        <v>289.8365398537936</v>
       </c>
       <c r="H16" t="n">
-        <v>192.9671090512441</v>
+        <v>311.8431250131912</v>
       </c>
       <c r="I16" t="n">
-        <v>266.589987987327</v>
+        <v>385.4660039492741</v>
       </c>
       <c r="J16" t="n">
-        <v>480.1637286397784</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="K16" t="n">
-        <v>480.1637286397784</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="L16" t="n">
-        <v>480.1637286397784</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="M16" t="n">
-        <v>207.8085656068997</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>207.8085656068997</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>207.8085656068997</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>207.8085656068997</v>
+        <v>545.5261898799506</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.12</v>
+        <v>545.5261898799506</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5472,7 +5472,7 @@
         <v>283.9399739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>247.1062842199767</v>
+        <v>283.9399739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5494,7 +5494,7 @@
         <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.0153761373309</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5509,22 +5509,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>520.2108514963016</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1326.070851496302</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M17" t="n">
-        <v>1836.919680225237</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N17" t="n">
-        <v>2450.14</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="O17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5585,16 +5585,16 @@
         <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>404.4452825072959</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>593.6380986016793</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>864.9885601968793</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M18" t="n">
-        <v>951.0691019397386</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N18" t="n">
         <v>1084.349386547307</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>405.793354586564</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C19" t="n">
-        <v>412.0053604049997</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D19" t="n">
-        <v>405.4031199448427</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E19" t="n">
-        <v>405.4031199448427</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F19" t="n">
-        <v>409.9740925367782</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G19" t="n">
-        <v>443.5906584236635</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H19" t="n">
-        <v>493.317243583061</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I19" t="n">
-        <v>594.6601225191439</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J19" t="n">
-        <v>835.9538631715952</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K19" t="n">
-        <v>826.3369199381174</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>826.3369199381174</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M19" t="n">
-        <v>826.3369199381174</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N19" t="n">
-        <v>826.3369199381174</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O19" t="n">
-        <v>826.3369199381174</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>601.4589976606127</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q19" t="n">
-        <v>601.4589976606127</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R19" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="S19" t="n">
         <v>65.12</v>
@@ -5709,7 +5709,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>413.989112502805</v>
+        <v>422.5399739669084</v>
       </c>
     </row>
     <row r="20">
@@ -5746,19 +5746,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.135479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1971.995479385524</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M20" t="n">
-        <v>1971.995479385524</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N20" t="n">
-        <v>2585.215799160287</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>2585.215799160287</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P20" t="n">
         <v>2817.400904947332</v>
@@ -5819,28 +5819,28 @@
         <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>65.12</v>
+        <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>189.076520175299</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>378.2693362696824</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>649.6197978648825</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M21" t="n">
-        <v>735.7003396077417</v>
+        <v>951.0691019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>1145.19062421531</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1428.253365791451</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P21" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1816.992710260958</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>413.989112502805</v>
+        <v>405.793354586564</v>
       </c>
       <c r="C22" t="n">
-        <v>420.2011183212408</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="D22" t="n">
-        <v>420.2011183212408</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="E22" t="n">
-        <v>420.2011183212408</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="F22" t="n">
-        <v>424.7720909131763</v>
+        <v>416.5763329969353</v>
       </c>
       <c r="G22" t="n">
-        <v>458.3886568000616</v>
+        <v>450.1928988838205</v>
       </c>
       <c r="H22" t="n">
-        <v>508.1152419594592</v>
+        <v>499.9194840432181</v>
       </c>
       <c r="I22" t="n">
-        <v>609.4581208955422</v>
+        <v>601.2623629793011</v>
       </c>
       <c r="J22" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="K22" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="L22" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="M22" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="N22" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="O22" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="P22" t="n">
-        <v>438.1782278830667</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R22" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S22" t="n">
         <v>65.12</v>
@@ -5983,19 +5983,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1166.135479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1693.331756443634</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>2204.180585172569</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N23" t="n">
-        <v>2817.400904947332</v>
+        <v>1205.680904947332</v>
       </c>
       <c r="O23" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P23" t="n">
         <v>2817.400904947332</v>
@@ -6022,7 +6022,7 @@
         <v>1635.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y23" t="n">
         <v>1085.153329539235</v>
@@ -6056,28 +6056,28 @@
         <v>65.12</v>
       </c>
       <c r="I24" t="n">
-        <v>65.12</v>
+        <v>126.374877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>189.076520175299</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>378.2693362696824</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>925.8297978648825</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M24" t="n">
-        <v>1011.910339607742</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N24" t="n">
-        <v>1145.19062421531</v>
+        <v>930.2355021828749</v>
       </c>
       <c r="O24" t="n">
-        <v>1660.443075899029</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P24" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q24" t="n">
         <v>1816.992710260958</v>
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>413.989112502805</v>
+        <v>405.793354586564</v>
       </c>
       <c r="C25" t="n">
-        <v>420.2011183212408</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="D25" t="n">
-        <v>420.2011183212408</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="E25" t="n">
-        <v>420.2011183212408</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="F25" t="n">
-        <v>424.7720909131763</v>
+        <v>416.5763329969353</v>
       </c>
       <c r="G25" t="n">
-        <v>458.3886568000616</v>
+        <v>450.1928988838205</v>
       </c>
       <c r="H25" t="n">
-        <v>508.1152419594592</v>
+        <v>499.9194840432181</v>
       </c>
       <c r="I25" t="n">
-        <v>609.4581208955422</v>
+        <v>601.2623629793011</v>
       </c>
       <c r="J25" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="K25" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="L25" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="M25" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="N25" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="O25" t="n">
-        <v>850.7518615479935</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="P25" t="n">
-        <v>517.2433615971223</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="Q25" t="n">
-        <v>517.2433615971223</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R25" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>696.8538895501313</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="C26" t="n">
-        <v>614.4725118488823</v>
+        <v>61.84</v>
       </c>
       <c r="D26" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="E26" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="F26" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6217,22 +6217,22 @@
         <v>61.84</v>
       </c>
       <c r="J26" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K26" t="n">
-        <v>1162.855479385524</v>
+        <v>764.0617564436058</v>
       </c>
       <c r="L26" t="n">
-        <v>1928.125479385524</v>
+        <v>764.0617564436058</v>
       </c>
       <c r="M26" t="n">
-        <v>2438.974308114459</v>
+        <v>1274.910585172541</v>
       </c>
       <c r="N26" t="n">
-        <v>2438.974308114459</v>
+        <v>1888.130904947304</v>
       </c>
       <c r="O26" t="n">
-        <v>2438.974308114459</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6241,28 +6241,28 @@
         <v>3092</v>
       </c>
       <c r="R26" t="n">
-        <v>3092</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2819.426093128967</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2454.097222696074</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2025.590862545962</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1616.650434094625</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1616.650434094625</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1245.658683124253</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>956.4491551618228</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6299,10 +6299,10 @@
         <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
         <v>1427.390920121557</v>
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>127.3309448365277</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>66.18324983091611</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>66.18324983091611</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>66.18324983091611</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>66.18324983091611</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>62.37403154645285</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I28" t="n">
-        <v>110.2569104825358</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J28" t="n">
-        <v>298.0906511349871</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>298.0906511349871</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>298.0906511349871</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>298.0906511349871</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>298.0906511349871</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="R28" t="n">
         <v>61.84</v>
@@ -6414,13 +6414,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>934.6792604187217</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="C29" t="n">
-        <v>707.9372621934754</v>
+        <v>61.84</v>
       </c>
       <c r="D29" t="n">
-        <v>520.7259937693847</v>
+        <v>61.84</v>
       </c>
       <c r="E29" t="n">
-        <v>520.7259937693847</v>
+        <v>61.84</v>
       </c>
       <c r="F29" t="n">
-        <v>339.0192981047262</v>
+        <v>61.84</v>
       </c>
       <c r="G29" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6457,22 +6457,22 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>1122.860904947265</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>1122.860904947265</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>1122.860904947265</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>1122.860904947265</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O29" t="n">
-        <v>1888.130904947299</v>
+        <v>3052.194627889258</v>
       </c>
       <c r="P29" t="n">
-        <v>2653.400904947332</v>
+        <v>3052.194627889258</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3065.860001183541</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>2700.531130750648</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2272.024770600536</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>2272.024770600536</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W29" t="n">
-        <v>1854.475804963215</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X29" t="n">
-        <v>1483.484053992844</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y29" t="n">
-        <v>1194.274526030413</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="30">
@@ -6530,28 +6530,28 @@
         <v>61.84</v>
       </c>
       <c r="I30" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>408.546520175299</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>820.4893362696823</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1314.589797864882</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1623.420339607742</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1979.45062421531</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2441.243075899029</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
-        <v>2631.894528442776</v>
+        <v>2580.493000882351</v>
       </c>
       <c r="Q30" t="n">
         <v>2631.894528442776</v>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H31" t="n">
-        <v>175.5382646830375</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I31" t="n">
-        <v>223.4211436191204</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="N31" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="O31" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="P31" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="Q31" t="n">
         <v>61.84</v>
@@ -6651,13 +6651,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="X31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6667,46 +6667,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C32" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D32" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E32" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F32" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G32" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H32" t="n">
-        <v>61.84</v>
+        <v>70.38201150041843</v>
       </c>
       <c r="I32" t="n">
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637026</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K32" t="n">
-        <v>1155.056868702875</v>
+        <v>654.8867607574315</v>
       </c>
       <c r="L32" t="n">
-        <v>1920.326868702875</v>
+        <v>1420.156760757432</v>
       </c>
       <c r="M32" t="n">
-        <v>1904.788787894794</v>
+        <v>1925.839809149365</v>
       </c>
       <c r="N32" t="n">
-        <v>2514.921883267472</v>
+        <v>1910.301728341283</v>
       </c>
       <c r="O32" t="n">
-        <v>2675.571728341327</v>
+        <v>1894.763647533202</v>
       </c>
       <c r="P32" t="n">
         <v>2660.033647533245</v>
@@ -6736,7 +6736,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y32" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="33">
@@ -6767,28 +6767,28 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>185.796520175299</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>374.9893362696823</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L33" t="n">
-        <v>934.4297978648825</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1020.510339607742</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>1280.322732289551</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>1519.36518397327</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
-        <v>1631.894528442776</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6828,52 +6828,52 @@
         <v>486.0066123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I34" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M34" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N34" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>524.9700332905304</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P34" t="n">
-        <v>524.9700332905304</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q34" t="n">
-        <v>133.9344239422782</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R34" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S34" t="n">
         <v>61.84</v>
@@ -6928,22 +6928,22 @@
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>61.84</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>771.3406764391767</v>
+        <v>430.9405883765129</v>
       </c>
       <c r="L35" t="n">
-        <v>1536.610676439177</v>
+        <v>415.402507568432</v>
       </c>
       <c r="M35" t="n">
-        <v>2042.29372483111</v>
+        <v>921.0855559603658</v>
       </c>
       <c r="N35" t="n">
-        <v>2026.755644023028</v>
+        <v>1129.493647533145</v>
       </c>
       <c r="O35" t="n">
-        <v>2011.217563214946</v>
+        <v>1894.763647533195</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -7013,19 +7013,19 @@
         <v>448.1242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>1007.564675832448</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M36" t="n">
-        <v>1093.645217575307</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N36" t="n">
-        <v>1226.925502182875</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O36" t="n">
-        <v>1519.36518397327</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P36" t="n">
-        <v>1631.894528442776</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7062,52 +7062,52 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I37" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="N37" t="n">
-        <v>728.8166160835463</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="O37" t="n">
-        <v>728.8166160835463</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="P37" t="n">
-        <v>501.0715822480788</v>
+        <v>611.3794220870118</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.84</v>
+        <v>172.147839838933</v>
       </c>
       <c r="R37" t="n">
         <v>61.84</v>
@@ -7131,7 +7131,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y37" t="n">
-        <v>482.1592746459407</v>
+        <v>482.1592746459644</v>
       </c>
     </row>
     <row r="38">
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
         <v>644.0209141871454</v>
@@ -7165,52 +7165,52 @@
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>77.37808080808094</v>
+        <v>61.84</v>
       </c>
       <c r="K38" t="n">
-        <v>61.84</v>
+        <v>771.3406764391794</v>
       </c>
       <c r="L38" t="n">
-        <v>781.676852755583</v>
+        <v>1536.610676439179</v>
       </c>
       <c r="M38" t="n">
-        <v>1287.359901147516</v>
+        <v>1521.072595631097</v>
       </c>
       <c r="N38" t="n">
-        <v>1897.492996520196</v>
+        <v>1505.534514823015</v>
       </c>
       <c r="O38" t="n">
-        <v>2326.729999999945</v>
+        <v>2270.804514823073</v>
       </c>
       <c r="P38" t="n">
-        <v>3092</v>
+        <v>3036.07451482313</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7241,25 +7241,25 @@
         <v>61.84</v>
       </c>
       <c r="I39" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>185.796520175299</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>384.7799167834979</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>656.130378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M39" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N39" t="n">
-        <v>1163.581204729126</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O39" t="n">
-        <v>1402.623656412844</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P39" t="n">
         <v>1515.153000882351</v>
@@ -7299,49 +7299,49 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122601</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306959</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>509.507762255696</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E40" t="n">
-        <v>519.426666467109</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590446</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459298</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053274</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I40" t="n">
-        <v>756.2036690414103</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693862</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M40" t="n">
-        <v>779.8807210018917</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N40" t="n">
-        <v>779.8807210018917</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O40" t="n">
-        <v>501.8421494759102</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P40" t="n">
-        <v>501.8421494759102</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q40" t="n">
         <v>501.8421494759102</v>
@@ -7368,7 +7368,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y40" t="n">
-        <v>482.159274645968</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>836.8521343108956</v>
+        <v>1276.823518472998</v>
       </c>
       <c r="C41" t="n">
-        <v>597.9889239644372</v>
+        <v>1037.960308126539</v>
       </c>
       <c r="D41" t="n">
-        <v>448.3521222172001</v>
+        <v>838.6278275812365</v>
       </c>
       <c r="E41" t="n">
-        <v>448.3521222172001</v>
+        <v>645.3315754530863</v>
       </c>
       <c r="F41" t="n">
-        <v>254.5242144313295</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7402,52 +7402,52 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>764.0617564435698</v>
       </c>
       <c r="L41" t="n">
-        <v>1202.66085149624</v>
+        <v>764.0617564435698</v>
       </c>
       <c r="M41" t="n">
-        <v>1713.509680225175</v>
+        <v>1274.910585172505</v>
       </c>
       <c r="N41" t="n">
-        <v>2326.729999999938</v>
+        <v>1888.130904947268</v>
       </c>
       <c r="O41" t="n">
-        <v>2326.729999999938</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3053.738789062329</v>
+        <v>3083.71551771221</v>
       </c>
       <c r="S41" t="n">
-        <v>2769.043670070084</v>
+        <v>3083.71551771221</v>
       </c>
       <c r="T41" t="n">
-        <v>2391.593587515979</v>
+        <v>3083.71551771221</v>
       </c>
       <c r="U41" t="n">
-        <v>1950.966015244655</v>
+        <v>3083.71551771221</v>
       </c>
       <c r="V41" t="n">
-        <v>1950.966015244655</v>
+        <v>2662.653877139661</v>
       </c>
       <c r="W41" t="n">
-        <v>1521.295837486122</v>
+        <v>2232.983699381128</v>
       </c>
       <c r="X41" t="n">
-        <v>1138.182874394538</v>
+        <v>1849.870736289544</v>
       </c>
       <c r="Y41" t="n">
-        <v>836.8521343108956</v>
+        <v>1548.539996205901</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>840.8840019843029</v>
+        <v>845.0520685412207</v>
       </c>
       <c r="C42" t="n">
-        <v>691.2881308272127</v>
+        <v>695.4561973841305</v>
       </c>
       <c r="D42" t="n">
-        <v>554.9874369911495</v>
+        <v>559.1555035480673</v>
       </c>
       <c r="E42" t="n">
-        <v>424.0055206053792</v>
+        <v>428.1735871622969</v>
       </c>
       <c r="F42" t="n">
-        <v>296.0901243044934</v>
+        <v>300.2581908614112</v>
       </c>
       <c r="G42" t="n">
-        <v>182.2118052388092</v>
+        <v>186.379871795727</v>
       </c>
       <c r="H42" t="n">
-        <v>61.84</v>
+        <v>66.00806655691771</v>
       </c>
       <c r="I42" t="n">
         <v>61.84</v>
@@ -7493,40 +7493,40 @@
         <v>1575.900339607742</v>
       </c>
       <c r="N42" t="n">
-        <v>1920.05062421531</v>
+        <v>1882.855659943693</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2332.768111627412</v>
       </c>
       <c r="P42" t="n">
-        <v>2512.38707571834</v>
+        <v>2656.167456096918</v>
       </c>
       <c r="Q42" t="n">
-        <v>2551.908603278765</v>
+        <v>2695.688983657343</v>
       </c>
       <c r="R42" t="n">
-        <v>2214.258302983432</v>
+        <v>2358.03868336201</v>
       </c>
       <c r="S42" t="n">
-        <v>1998.348124233868</v>
+        <v>2101.913430872504</v>
       </c>
       <c r="T42" t="n">
-        <v>1804.047351286884</v>
+        <v>1907.612657925521</v>
       </c>
       <c r="U42" t="n">
-        <v>1614.945977791746</v>
+        <v>1718.511284430382</v>
       </c>
       <c r="V42" t="n">
-        <v>1411.399849315463</v>
+        <v>1514.965155954099</v>
       </c>
       <c r="W42" t="n">
-        <v>1411.399849315463</v>
+        <v>1415.567915872381</v>
       </c>
       <c r="X42" t="n">
-        <v>1202.447587249415</v>
+        <v>1206.615653806333</v>
       </c>
       <c r="Y42" t="n">
-        <v>1014.173453142209</v>
+        <v>1018.341519699126</v>
       </c>
     </row>
     <row r="43">
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="C43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="D43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="E43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="F43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="H43" t="n">
         <v>61.84</v>
@@ -7560,52 +7560,52 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="K43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="L43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="M43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="N43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="O43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="P43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>237.7937406524513</v>
+        <v>61.84</v>
       </c>
       <c r="R43" t="n">
-        <v>81.88763509199777</v>
+        <v>61.84</v>
       </c>
       <c r="S43" t="n">
-        <v>81.88763509199777</v>
+        <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>84.83331425080263</v>
+        <v>61.84</v>
       </c>
       <c r="U43" t="n">
-        <v>146.2545068890893</v>
+        <v>61.84</v>
       </c>
       <c r="V43" t="n">
-        <v>159.9458997750352</v>
+        <v>61.84</v>
       </c>
       <c r="W43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="X43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
       <c r="Y43" t="n">
-        <v>146.4380110490658</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="44">
@@ -7615,16 +7615,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1100.612139363444</v>
+        <v>1225.637553827664</v>
       </c>
       <c r="C44" t="n">
-        <v>835.4863027543594</v>
+        <v>960.5117172185788</v>
       </c>
       <c r="D44" t="n">
-        <v>609.8911959464303</v>
+        <v>734.9166104106498</v>
       </c>
       <c r="E44" t="n">
-        <v>504.0289201924683</v>
+        <v>515.3577320198734</v>
       </c>
       <c r="F44" t="n">
         <v>504.0289201924683</v>
@@ -7645,13 +7645,13 @@
         <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>1536.816366347868</v>
+        <v>1529.331756443634</v>
       </c>
       <c r="M44" t="n">
-        <v>1888.130904947256</v>
+        <v>2040.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>1888.130904947256</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O44" t="n">
         <v>2653.400904947332</v>
@@ -7669,22 +7669,22 @@
         <v>2716.518417544831</v>
       </c>
       <c r="T44" t="n">
-        <v>2312.8057087281</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="U44" t="n">
-        <v>1845.91551019415</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="V44" t="n">
-        <v>1398.591243358974</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="W44" t="n">
-        <v>1398.591243358974</v>
+        <v>2260.585613523672</v>
       </c>
       <c r="X44" t="n">
-        <v>1398.591243358974</v>
+        <v>1851.210024169462</v>
       </c>
       <c r="Y44" t="n">
-        <v>1398.591243358974</v>
+        <v>1523.616657823193</v>
       </c>
     </row>
     <row r="45">
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>874.7124298160925</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="C45" t="n">
-        <v>698.853932396376</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="D45" t="n">
-        <v>536.2906122976865</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="E45" t="n">
-        <v>379.04606964929</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="F45" t="n">
         <v>379.04606964929</v>
@@ -7736,34 +7736,34 @@
         <v>2215.523075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>2389.507571919719</v>
+        <v>2346.873102759523</v>
       </c>
       <c r="Q45" t="n">
-        <v>2403.289099480144</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="R45" t="n">
-        <v>2039.376172922185</v>
+        <v>1996.741703761989</v>
       </c>
       <c r="S45" t="n">
-        <v>1787.679737777241</v>
+        <v>1770.293626357847</v>
       </c>
       <c r="T45" t="n">
-        <v>1787.679737777241</v>
+        <v>1549.730227148237</v>
       </c>
       <c r="U45" t="n">
-        <v>1572.315738019477</v>
+        <v>1334.366227390473</v>
       </c>
       <c r="V45" t="n">
-        <v>1572.315738019477</v>
+        <v>1104.557472651563</v>
       </c>
       <c r="W45" t="n">
-        <v>1324.4640785146</v>
+        <v>1104.557472651563</v>
       </c>
       <c r="X45" t="n">
-        <v>1089.249190185925</v>
+        <v>1104.557472651563</v>
       </c>
       <c r="Y45" t="n">
-        <v>874.7124298160925</v>
+        <v>890.0207122817305</v>
       </c>
     </row>
     <row r="46">
@@ -7794,46 +7794,46 @@
         <v>61.84</v>
       </c>
       <c r="I46" t="n">
-        <v>72.10287893608292</v>
+        <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="K46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="L46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="M46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="N46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="O46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="P46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="Q46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="R46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="S46" t="n">
-        <v>72.10287893608292</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="T46" t="n">
-        <v>72.10287893608292</v>
+        <v>156.0968142995399</v>
       </c>
       <c r="U46" t="n">
-        <v>104.0330566683016</v>
+        <v>156.0968142995399</v>
       </c>
       <c r="V46" t="n">
-        <v>104.0330566683016</v>
+        <v>143.8035716568973</v>
       </c>
       <c r="W46" t="n">
         <v>104.0330566683016</v>
@@ -7964,16 +7964,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>65.90862873094373</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>747.1165439402098</v>
       </c>
       <c r="N2" t="n">
         <v>1096.663422488788</v>
@@ -8201,13 +8201,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K5" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>163.0335112078408</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
@@ -8216,10 +8216,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409606</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>598.2574409074563</v>
+        <v>0.2870600406851054</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8453,10 +8453,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409242</v>
+        <v>233.2813807819365</v>
       </c>
       <c r="P8" t="n">
-        <v>501.1325584305591</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8693,7 +8693,7 @@
         <v>231.79875049407</v>
       </c>
       <c r="P11" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
         <v>172.8226843274854</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>134.6738680171692</v>
+        <v>184.0310918930479</v>
       </c>
       <c r="P14" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,7 +9152,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>64.42599844307665</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>814</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>884.2478695740924</v>
+        <v>505.644479075081</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,22 +9389,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>814</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>311.0589434940335</v>
       </c>
       <c r="P20" t="n">
-        <v>234.8174699265858</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9626,22 +9626,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1096.663422488788</v>
+        <v>718.0600319897761</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>709.3149054985918</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741213</v>
       </c>
       <c r="P26" t="n">
-        <v>216.8795820940887</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>676.476557484454</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>843.2478695741263</v>
+        <v>843.2478695741286</v>
       </c>
       <c r="P29" t="n">
-        <v>773.2870600407153</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>213.0301309039922</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,22 +10337,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>221.706710657106</v>
       </c>
       <c r="L32" t="n">
-        <v>773.0000000000002</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>244.6739161972097</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407249</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,25 +10571,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>50.42570624509119</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>772.9999999999998</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>698.9556687268873</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741431</v>
       </c>
       <c r="P35" t="n">
-        <v>657.9976835157983</v>
+        <v>773.2870600407322</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>65.80840624509153</v>
+        <v>50.42570624509142</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>727.1079320763464</v>
+        <v>772.9999999999998</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>510.5752030190453</v>
+        <v>843.2478695741504</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407372</v>
+        <v>773.2870600407394</v>
       </c>
       <c r="Q38" t="n">
-        <v>188.2053843274866</v>
+        <v>243.5716146525881</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>314.053175157489</v>
       </c>
       <c r="L41" t="n">
-        <v>435.4691769175466</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,13 +11060,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741577</v>
       </c>
       <c r="P41" t="n">
-        <v>773.2870600407444</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11288,16 +11288,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
-        <v>899.1252979447288</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>843.24786957417</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -22700,10 +22700,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696443673</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>29.21007785422643</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>29.21007785422375</v>
+        <v>29.21007785422779</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,13 +23174,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696451105</v>
       </c>
       <c r="N10" t="n">
-        <v>29.21007785422898</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -23232,16 +23232,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>179.3305386072528</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23280,13 +23280,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>6.56278315153628</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>346.1850752716849</v>
@@ -23423,13 +23423,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>462.4478973282775</v>
+        <v>417.3027092422997</v>
       </c>
       <c r="Q13" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>159.4525186539137</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23469,13 +23469,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>86.30994672070055</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23517,7 +23517,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>238.540979906574</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -23618,10 +23618,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
         <v>34.53621805555548</v>
@@ -23630,7 +23630,7 @@
         <v>29.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
         <v>320.1850752716849</v>
@@ -23660,13 +23660,13 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>383.4694781537204</v>
       </c>
       <c r="Q16" t="n">
-        <v>333.5775864747674</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23709,10 +23709,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.4306086145859922</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4306086145860206</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23855,13 +23855,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
         <v>1.98090483695654</v>
@@ -23882,7 +23882,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
         <v>144.5476281577792</v>
@@ -23897,16 +23897,16 @@
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>185.8187542735478</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="20">
@@ -24092,7 +24092,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -24134,16 +24134,16 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>77.51162082136199</v>
+        <v>208.1531315141696</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24237,10 +24237,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.4306086145858785</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>0.430608614578091</v>
       </c>
     </row>
     <row r="24">
@@ -24329,7 +24329,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -24371,16 +24371,16 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>78.27448237691499</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>208.1531315141696</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24411,10 +24411,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>142.9170143187574</v>
+        <v>35.06290239760591</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
@@ -24423,10 +24423,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24456,7 +24456,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -24471,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24569,10 +24569,10 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
         <v>55.98090483695654</v>
@@ -24605,7 +24605,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>181.5574194553778</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>462.4478973282775</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24648,22 +24648,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>35.06290239760591</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>87.3595258668647</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2643398428289174</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O31" t="n">
         <v>415.445564079015</v>
@@ -24848,7 +24848,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R31" t="n">
         <v>501.6021279811511</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
         <v>229.6316114025499</v>
@@ -25079,19 +25079,19 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q34" t="n">
-        <v>47.71401317082831</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25313,19 +25313,19 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>170.9803138311647</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>326.3973665406074</v>
       </c>
       <c r="S37" t="n">
         <v>71.37347970285543</v>
@@ -25547,19 +25547,19 @@
         <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
         <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>74.18737826829323</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -25593,16 +25593,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>49.19872201008508</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -25611,7 +25611,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,19 +25641,19 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>29.67696136338276</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25693,7 +25693,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4.126385891348534</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25723,7 +25723,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>39.81292300254248</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>219.3731429098285</v>
+        <v>120.9698752289271</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25760,7 +25760,7 @@
         <v>72.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>67.98090483695654</v>
       </c>
       <c r="F43" t="n">
         <v>61.38285596774193</v>
@@ -25769,7 +25769,7 @@
         <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25799,7 +25799,7 @@
         <v>512.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>359.255083476302</v>
+        <v>513.6021279811511</v>
       </c>
       <c r="S43" t="n">
         <v>149.3734797028554</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>13.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>34.44364543010755</v>
@@ -25839,10 +25839,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>112.5596366104462</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>206.6741049988808</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -25884,22 +25884,22 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>451.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>324.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -25909,19 +25909,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>197.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -25960,22 +25960,22 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>30.38452917111701</v>
+        <v>55.38040333451102</v>
       </c>
       <c r="T45" t="n">
-        <v>218.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>227.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>232.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -26042,16 +26042,16 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5458542.889777285</v>
+        <v>5458542.889777286</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6220515.38513987</v>
+        <v>6220515.385139872</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6912813.964875257</v>
+        <v>6912813.964875258</v>
       </c>
     </row>
     <row r="11">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8376273.704984931</v>
+        <v>8376273.704984929</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10582549.82516827</v>
+        <v>10582549.82516826</v>
       </c>
     </row>
     <row r="16">
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1416010.498272106</v>
+      </c>
+      <c r="C2" t="n">
         <v>1416010.498272105</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1416010.498272106</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1416010.498272105</v>
       </c>
       <c r="E2" t="n">
         <v>1266782.650763704</v>
@@ -26299,13 +26299,13 @@
         <v>1252534.099523703</v>
       </c>
       <c r="L2" t="n">
+        <v>1379280.490794997</v>
+      </c>
+      <c r="M2" t="n">
         <v>1379280.490794998</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1379280.490794997</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1379280.490794998</v>
       </c>
       <c r="O2" t="n">
         <v>1215148.976618704</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575615.820517953</v>
+        <v>580502.372390945</v>
       </c>
       <c r="C4" t="n">
-        <v>573863.9117786936</v>
+        <v>578750.4636516855</v>
       </c>
       <c r="D4" t="n">
-        <v>572109.6264658828</v>
+        <v>576996.1783388747</v>
       </c>
       <c r="E4" t="n">
-        <v>493887.8206072089</v>
+        <v>498724.2862854869</v>
       </c>
       <c r="F4" t="n">
-        <v>518162.4364012047</v>
+        <v>522998.9020794826</v>
       </c>
       <c r="G4" t="n">
-        <v>542951.8445255278</v>
+        <v>547788.3102038057</v>
       </c>
       <c r="H4" t="n">
-        <v>541278.9095854305</v>
+        <v>546115.3752637085</v>
       </c>
       <c r="I4" t="n">
-        <v>539603.6392010038</v>
+        <v>544440.1048792822</v>
       </c>
       <c r="J4" t="n">
-        <v>483069.4589672089</v>
+        <v>487781.687779115</v>
       </c>
       <c r="K4" t="n">
-        <v>481604.7173132672</v>
+        <v>486316.9461251732</v>
       </c>
       <c r="L4" t="n">
-        <v>543419.7365500291</v>
+        <v>548178.8299014303</v>
       </c>
       <c r="M4" t="n">
-        <v>541689.6178484762</v>
+        <v>546448.711199878</v>
       </c>
       <c r="N4" t="n">
-        <v>539957.0115239245</v>
+        <v>544716.1048753252</v>
       </c>
       <c r="O4" t="n">
-        <v>457615.9305970518</v>
+        <v>462328.1594089579</v>
       </c>
       <c r="P4" t="n">
-        <v>416810.1932019159</v>
+        <v>421522.4220138221</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>470747.8777541523</v>
+        <v>465861.3258811606</v>
       </c>
       <c r="C6" t="n">
-        <v>759027.7864934122</v>
+        <v>754141.2346204196</v>
       </c>
       <c r="D6" t="n">
-        <v>760782.0718062224</v>
+        <v>755895.5199332309</v>
       </c>
       <c r="E6" t="n">
-        <v>524488.1051564947</v>
+        <v>519651.6394782166</v>
       </c>
       <c r="F6" t="n">
-        <v>708889.1880679211</v>
+        <v>704052.7223896432</v>
       </c>
       <c r="G6" t="n">
-        <v>733252.1961271327</v>
+        <v>728415.7304488549</v>
       </c>
       <c r="H6" t="n">
-        <v>757325.1310672307</v>
+        <v>752488.665388952</v>
       </c>
       <c r="I6" t="n">
-        <v>759000.4014516569</v>
+        <v>754163.9357733788</v>
       </c>
       <c r="J6" t="n">
-        <v>294654.7155564944</v>
+        <v>289942.4867445883</v>
       </c>
       <c r="K6" t="n">
-        <v>684215.4572104362</v>
+        <v>679503.2283985298</v>
       </c>
       <c r="L6" t="n">
-        <v>689198.2752449687</v>
+        <v>684439.1818935669</v>
       </c>
       <c r="M6" t="n">
-        <v>766128.3939465212</v>
+        <v>761369.3005951201</v>
       </c>
       <c r="N6" t="n">
-        <v>767861.0002710735</v>
+        <v>763101.9069196722</v>
       </c>
       <c r="O6" t="n">
-        <v>618227.9490216525</v>
+        <v>613515.7202097465</v>
       </c>
       <c r="P6" t="n">
-        <v>653883.3394195257</v>
+        <v>649171.1106076195</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27008,7 +27008,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27436,25 +27436,25 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>307.3903671255646</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -27496,13 +27496,13 @@
         <v>400</v>
       </c>
       <c r="W2" t="n">
+        <v>306.4306086145855</v>
+      </c>
+      <c r="X2" t="n">
         <v>400</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>115.3536407070568</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>158.7921542740601</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,22 +27594,22 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>384.5496695326865</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
@@ -27645,16 +27645,16 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U4" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V4" t="n">
+        <v>225.818750308082</v>
+      </c>
+      <c r="W4" t="n">
         <v>400</v>
-      </c>
-      <c r="U4" t="n">
-        <v>400</v>
-      </c>
-      <c r="V4" t="n">
-        <v>400</v>
-      </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
@@ -27679,17 +27679,17 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>400</v>
       </c>
-      <c r="G5" t="n">
-        <v>307.3903671255645</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -27721,10 +27721,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>307.3903671255646</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27739,7 +27739,7 @@
         <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>193.9840721817118</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27809,13 +27809,13 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>303.3742880620965</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27831,13 +27831,13 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>384.1281642552216</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
@@ -27849,13 +27849,13 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>225.1413562431383</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27907,10 +27907,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.3092074428801</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27919,10 +27919,10 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>157.3092074428801</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
@@ -27958,7 +27958,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27970,13 +27970,13 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>229.1138239371239</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28001,7 +28001,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28040,19 +28040,19 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>342.2743756165772</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,31 +28065,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>365.4196423280227</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28122,16 +28122,16 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
+        <v>152.3124856566939</v>
+      </c>
+      <c r="V10" t="n">
         <v>400</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28244,10 +28244,10 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>26.99048536749038</v>
+        <v>19.11687125883891</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28481,31 +28481,31 @@
         <v>251</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>251</v>
       </c>
       <c r="J15" t="n">
         <v>251</v>
       </c>
       <c r="K15" t="n">
+        <v>166.1982915220775</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>251</v>
       </c>
-      <c r="L15" t="n">
+      <c r="P15" t="n">
         <v>251</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>251</v>
-      </c>
-      <c r="O15" t="n">
-        <v>26.99264054024954</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28721,19 +28721,19 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>155.6705902671031</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>279</v>
@@ -28955,7 +28955,7 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28967,19 +28967,19 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="N21" t="n">
         <v>279</v>
       </c>
       <c r="O21" t="n">
-        <v>44.46493928527505</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>279</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29161,7 +29161,7 @@
         <v>279</v>
       </c>
       <c r="Y23" t="n">
-        <v>279</v>
+        <v>279.0000000000078</v>
       </c>
     </row>
     <row r="24">
@@ -29192,7 +29192,7 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29201,22 +29201,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>155.6705902671032</v>
+      </c>
+      <c r="P24" t="n">
         <v>279</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>279</v>
-      </c>
-      <c r="P24" t="n">
-        <v>44.46493928527515</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29435,13 +29435,13 @@
         <v>225</v>
       </c>
       <c r="K27" t="n">
-        <v>19.11687125883918</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29666,7 +29666,7 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J30" t="n">
         <v>225</v>
@@ -29681,16 +29681,16 @@
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>78.91122027701083</v>
+        <v>225</v>
       </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>291</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>141.6245682972704</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29872,7 +29872,7 @@
         <v>291</v>
       </c>
       <c r="Y32" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -29903,7 +29903,7 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29912,22 +29912,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>227.0158611578289</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>291</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>127.8102101760009</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -29964,7 +29964,7 @@
         <v>291</v>
       </c>
       <c r="C34" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="D34" t="n">
         <v>291</v>
@@ -30149,22 +30149,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>227.0158611578289</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>291</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>53.9365960673492</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30267,7 +30267,7 @@
         <v>291</v>
       </c>
       <c r="Y37" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
     </row>
     <row r="38">
@@ -30280,7 +30280,7 @@
         <v>291</v>
       </c>
       <c r="C38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="D38" t="n">
         <v>291</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30377,19 +30377,19 @@
         <v>291</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>9.889475266480332</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -30398,7 +30398,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="Q39" t="n">
         <v>291</v>
@@ -30504,7 +30504,7 @@
         <v>291</v>
       </c>
       <c r="Y40" t="n">
-        <v>291.0000000000276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41">
@@ -30629,13 +30629,13 @@
         <v>213</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>175.4293290185687</v>
       </c>
       <c r="O42" t="n">
         <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>30.19662156545908</v>
+        <v>213</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>213</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30726,13 +30726,13 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>213</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>213</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
-        <v>213</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30872,7 +30872,7 @@
         <v>187</v>
       </c>
       <c r="P45" t="n">
-        <v>62.07591065776113</v>
+        <v>19.01079029392661</v>
       </c>
       <c r="Q45" t="n">
         <v>187</v>
@@ -30930,10 +30930,10 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>187</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>35.26894883590776</v>
+        <v>153.9699106385832</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>183.2110960544769</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34749,7 +34749,7 @@
         <v>814</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34880,22 +34880,22 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>103.56876469573</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
         <v>223.3665443798817</v>
@@ -34931,16 +34931,16 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>26.64844009186581</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -34995,10 +34995,10 @@
         <v>814</v>
       </c>
       <c r="O5" t="n">
+        <v>814</v>
+      </c>
+      <c r="P5" t="n">
         <v>814.0000000000036</v>
-      </c>
-      <c r="P5" t="n">
-        <v>814</v>
       </c>
       <c r="Q5" t="n">
         <v>814</v>
@@ -35117,13 +35117,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>111.402917607177</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
@@ -35135,13 +35135,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>74.18296496868041</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35220,10 +35220,10 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>814</v>
@@ -35351,31 +35351,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78.30584199094409</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35408,16 +35408,16 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>1.354094382235957</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35460,7 +35460,7 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35472,7 +35472,7 @@
         <v>161.5508809199775</v>
       </c>
       <c r="P11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35530,10 +35530,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>152.1990916051661</v>
+        <v>144.3254774965146</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>64.42599844307681</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="P14" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
         <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>442.1038546407913</v>
+        <v>357.3021461628688</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>268.4496624429959</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>113.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>64.42599844307665</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>814</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>814</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,7 +36007,7 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>280.8791965047788</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>191.1038546407913</v>
@@ -36019,7 +36019,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757579</v>
       </c>
       <c r="O18" t="n">
         <v>520.4570219027464</v>
@@ -36168,22 +36168,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>814</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>240.811073919941</v>
       </c>
       <c r="P20" t="n">
-        <v>234.5304098859044</v>
+        <v>814</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36241,7 +36241,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
@@ -36253,19 +36253,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>86.95004216450428</v>
+        <v>242.6206324316074</v>
       </c>
       <c r="N21" t="n">
         <v>413.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>285.9219611880214</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36405,22 +36405,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>619.4144644189528</v>
+        <v>240.8110739199409</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
         <v>125.2086062376757</v>
@@ -36487,7 +36487,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>553.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
         <v>86.95004216450428</v>
@@ -36496,13 +36496,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>397.1276121698496</v>
       </c>
       <c r="P24" t="n">
-        <v>158.1309437999284</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>709.3149054985918</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>773.0000000000289</v>
       </c>
       <c r="P26" t="n">
-        <v>216.5925220534073</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36721,13 +36721,13 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>676.476557484454</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>773.0000000000339</v>
+        <v>773.0000000000362</v>
       </c>
       <c r="P29" t="n">
-        <v>773.0000000000339</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>40.20744657650677</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
         <v>350.2086062376757</v>
@@ -36967,16 +36967,16 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>192.577224791664</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320762964</v>
+        <v>727.1079320760909</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000434</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37198,13 +37198,13 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>565.0913753486871</v>
+        <v>501.1072365065158</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>262.4367602846557</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37250,7 +37250,7 @@
         <v>3.886199662921342</v>
       </c>
       <c r="C34" t="n">
-        <v>18.27475335197925</v>
+        <v>18.27475335195533</v>
       </c>
       <c r="D34" t="n">
         <v>5.46378194444452</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000507</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320761005</v>
+        <v>727.1079320762562</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000507</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000507</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000507</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000507</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000507</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,7 +37435,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>565.0913753486871</v>
+        <v>501.1072365065158</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37444,13 +37444,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>295.3936179700956</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37553,7 +37553,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.534647150537637</v>
+        <v>3.534647150561582</v>
       </c>
     </row>
     <row r="38">
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.000000000058</v>
       </c>
       <c r="K38" t="n">
+        <v>727.1079320759661</v>
+      </c>
+      <c r="L38" t="n">
         <v>773</v>
       </c>
-      <c r="L38" t="n">
-        <v>727.1079320763466</v>
-      </c>
       <c r="M38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.000000000058</v>
       </c>
       <c r="N38" t="n">
-        <v>773</v>
+        <v>773.000000000058</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.000000000058</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.000000000058</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.000000000058</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,19 +37663,19 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>200.9933299072716</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
-        <v>377.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
@@ -37684,7 +37684,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>340.6818656724819</v>
       </c>
       <c r="Q39" t="n">
         <v>117.9207349095204</v>
@@ -37790,7 +37790,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.53464715056522</v>
+        <v>3.534647150537637</v>
       </c>
     </row>
     <row r="41">
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>314.053175157489</v>
       </c>
       <c r="L41" t="n">
-        <v>435.4691769175466</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,13 +37839,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>773.0000000000653</v>
       </c>
       <c r="P41" t="n">
-        <v>773.000000000063</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37915,13 +37915,13 @@
         <v>299.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>347.6265501086548</v>
+        <v>310.0558791272235</v>
       </c>
       <c r="O42" t="n">
         <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>143.8626260801123</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>177.7310511640922</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38012,13 +38012,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.975433493742287</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>62.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>13.82968978378381</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38067,16 +38067,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
-        <v>354.8631703024114</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>773.0000000000775</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38158,7 +38158,7 @@
         <v>428.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>175.7419151724143</v>
+        <v>132.6767948085798</v>
       </c>
       <c r="Q45" t="n">
         <v>13.92073490952041</v>
@@ -38216,10 +38216,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>10.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>118.7009618026754</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>32.25270478001891</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
